--- a/output/pdf_financials_xlsx/KRN.xlsx
+++ b/output/pdf_financials_xlsx/KRN.xlsx
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.490823</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>59.000457</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.046161</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.04074</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.027733</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.016752</v>
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.490823</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>59.000457</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2357,13 +2357,13 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.046161</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.04074</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.027733</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.016752</v>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>8.855530999999999</v>
+        <v>6.364708</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>59.313322</v>
+        <v>0.312865</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.0463</v>
+        <v>0.000139</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.040901</v>
+        <v>0.000161</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.027982</v>
+        <v>0.000249</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.000327</v>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -12425,7 +12425,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">

--- a/output/pdf_financials_xlsx/KRN.xlsx
+++ b/output/pdf_financials_xlsx/KRN.xlsx
@@ -20896,7 +20896,11 @@
           <t>Additions to intangible assets (note 6)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -21705,7 +21709,11 @@
           <t>Additions to intangible assets (note 7)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -23521,7 +23529,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E178" s="5" t="n">
         <v>-2.822659</v>
       </c>
